--- a/data/trans_orig/Q5403-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q5403-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>832</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7934</t>
+          <t>7287</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6015</t>
+          <t>5774</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18993</t>
+          <t>18912</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7612</t>
+          <t>8346</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21937</t>
+          <t>22719</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6157</t>
+          <t>5624</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20042</t>
+          <t>18777</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23286</t>
+          <t>23026</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45271</t>
+          <t>43841</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31498</t>
+          <t>31854</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>56330</t>
+          <t>56662</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,92%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>269715</t>
+          <t>270171</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>284476</t>
+          <t>285092</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>285943</t>
+          <t>287165</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>311451</t>
+          <t>310285</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>563203</t>
+          <t>563852</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>592309</t>
+          <t>591884</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,13%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10987</t>
+          <t>11062</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25294</t>
+          <t>26464</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>31814</t>
+          <t>32438</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>57059</t>
+          <t>57565</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>47765</t>
+          <t>48161</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>77941</t>
+          <t>79136</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,55%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20940</t>
+          <t>20573</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>40038</t>
+          <t>39861</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>47964</t>
+          <t>49371</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>77741</t>
+          <t>80300</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>74229</t>
+          <t>73240</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>112044</t>
+          <t>108886</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,02%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>151568</t>
+          <t>150615</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>174285</t>
+          <t>174002</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>209919</t>
+          <t>210012</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>244468</t>
+          <t>245261</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>369962</t>
+          <t>369030</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>413481</t>
+          <t>412198</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>75,8%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13204</t>
+          <t>13707</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29372</t>
+          <t>30249</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>41819</t>
+          <t>42509</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>70741</t>
+          <t>73004</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>60298</t>
+          <t>58788</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>94026</t>
+          <t>92831</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28795</t>
+          <t>29398</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52318</t>
+          <t>53924</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>79436</t>
+          <t>78046</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>113814</t>
+          <t>114321</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>115493</t>
+          <t>112857</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>158559</t>
+          <t>157902</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,39%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>426981</t>
+          <t>426991</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>455129</t>
+          <t>454178</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>503019</t>
+          <t>504644</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>548479</t>
+          <t>548216</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>942631</t>
+          <t>941056</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>993334</t>
+          <t>996341</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,49%</t>
         </is>
       </c>
     </row>
@@ -2331,12 +2331,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7848</t>
+          <t>7186</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22364</t>
+          <t>21062</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2346,12 +2346,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2366,12 +2366,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11728</t>
+          <t>11493</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28436</t>
+          <t>30768</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2381,12 +2381,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2401,12 +2401,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21625</t>
+          <t>22072</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43895</t>
+          <t>44144</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2416,12 +2416,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -2444,12 +2444,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8386</t>
+          <t>9017</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25264</t>
+          <t>26542</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2459,12 +2459,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2479,12 +2479,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18283</t>
+          <t>19038</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39327</t>
+          <t>40585</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2514,12 +2514,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30585</t>
+          <t>31463</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57567</t>
+          <t>59528</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2529,12 +2529,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,97%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>269763</t>
+          <t>267788</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>290397</t>
+          <t>289990</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>292305</t>
+          <t>291830</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>319458</t>
+          <t>319112</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>571598</t>
+          <t>567748</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>605064</t>
+          <t>604340</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,05%</t>
         </is>
       </c>
     </row>
@@ -2787,12 +2787,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>26460</t>
+          <t>26609</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>51498</t>
+          <t>52101</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>77367</t>
+          <t>76109</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>111525</t>
+          <t>111969</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2837,12 +2837,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>111705</t>
+          <t>110938</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>153362</t>
+          <t>155523</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,35%</t>
         </is>
       </c>
     </row>
@@ -2900,12 +2900,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33915</t>
+          <t>33340</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>59955</t>
+          <t>57541</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>61105</t>
+          <t>60109</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>93587</t>
+          <t>92311</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>101208</t>
+          <t>99730</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>141140</t>
+          <t>141782</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,19%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>150915</t>
+          <t>151085</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>184136</t>
+          <t>184209</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>198473</t>
+          <t>200525</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>238895</t>
+          <t>240987</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>51,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>362180</t>
+          <t>359350</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>413099</t>
+          <t>413169</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,68%</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>37294</t>
+          <t>37541</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>66463</t>
+          <t>67310</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>94375</t>
+          <t>92968</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>133791</t>
+          <t>132744</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>138858</t>
+          <t>140410</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>189632</t>
+          <t>188604</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,48%</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45668</t>
+          <t>46133</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78135</t>
+          <t>77299</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>85697</t>
+          <t>86512</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>125859</t>
+          <t>124358</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>140707</t>
+          <t>140090</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>189923</t>
+          <t>190553</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,63%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>429023</t>
+          <t>428171</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>468177</t>
+          <t>469295</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>500031</t>
+          <t>501349</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>553212</t>
+          <t>552369</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>945843</t>
+          <t>944417</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1008660</t>
+          <t>1006310</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>72,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>77,25%</t>
         </is>
       </c>
     </row>
@@ -3929,12 +3929,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2975</t>
+          <t>3025</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14811</t>
+          <t>15512</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3944,49 +3944,49 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>4,64%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>9039</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4121</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>16751</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
           <t>4,43%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>9039</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>4211</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>17785</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>4,71%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>15</t>
@@ -3999,12 +3999,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>9292</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27333</t>
+          <t>26033</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4014,12 +4014,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -4042,12 +4042,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6174</t>
+          <t>6913</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21307</t>
+          <t>20453</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4057,12 +4057,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23903</t>
+          <t>24230</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46526</t>
+          <t>46305</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34398</t>
+          <t>33317</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59986</t>
+          <t>60155</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4127,12 +4127,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>304862</t>
+          <t>304208</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>322244</t>
+          <t>321906</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>319563</t>
+          <t>321909</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>346423</t>
+          <t>346522</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>632207</t>
+          <t>632427</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>663469</t>
+          <t>664012</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,25%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>23035</t>
+          <t>22197</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>41831</t>
+          <t>42143</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>47537</t>
+          <t>44941</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>80309</t>
+          <t>78071</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>75270</t>
+          <t>74461</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>115147</t>
+          <t>111808</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,01%</t>
         </is>
       </c>
     </row>
@@ -4498,12 +4498,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20552</t>
+          <t>21164</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>39252</t>
+          <t>39425</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>72525</t>
+          <t>72211</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>112351</t>
+          <t>110909</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4548,12 +4548,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>99669</t>
+          <t>100477</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>142783</t>
+          <t>142718</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4583,12 +4583,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,72%</t>
         </is>
       </c>
     </row>
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>183467</t>
+          <t>183728</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>208426</t>
+          <t>207973</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4646,12 +4646,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>223162</t>
+          <t>226720</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>268923</t>
+          <t>271069</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>56,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,2%</t>
+          <t>67,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>414797</t>
+          <t>417250</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>470403</t>
+          <t>469309</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>71,41%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29026</t>
+          <t>29997</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>51283</t>
+          <t>52359</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>55252</t>
+          <t>52682</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>89855</t>
+          <t>90772</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>89562</t>
+          <t>89065</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>132515</t>
+          <t>131769</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -4954,12 +4954,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30382</t>
+          <t>31087</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54753</t>
+          <t>54726</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4969,12 +4969,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>103029</t>
+          <t>102847</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>149657</t>
+          <t>147386</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>141247</t>
+          <t>143491</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>194030</t>
+          <t>192918</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,09%</t>
         </is>
       </c>
     </row>
@@ -5067,12 +5067,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>493153</t>
+          <t>494789</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>525251</t>
+          <t>525322</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>553202</t>
+          <t>552626</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>606809</t>
+          <t>609716</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1061009</t>
+          <t>1064110</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1122936</t>
+          <t>1125038</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,16%</t>
         </is>
       </c>
     </row>
@@ -5522,32 +5522,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>8956</t>
+          <t>9143</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5305</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14236</t>
+          <t>15113</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5557,32 +5557,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>15028</t>
+          <t>16876</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5872</t>
+          <t>11622</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26111</t>
+          <t>23773</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5592,32 +5592,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>23985</t>
+          <t>26019</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12526</t>
+          <t>18831</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35023</t>
+          <t>34796</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -5635,32 +5635,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20180</t>
+          <t>22069</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14335</t>
+          <t>14975</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27608</t>
+          <t>30024</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5670,32 +5670,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>38951</t>
+          <t>43302</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14347</t>
+          <t>34837</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62832</t>
+          <t>52867</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5705,32 +5705,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>59131</t>
+          <t>65371</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29238</t>
+          <t>54844</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>80391</t>
+          <t>78101</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>9,25%</t>
         </is>
       </c>
     </row>
@@ -5748,32 +5748,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>337872</t>
+          <t>374694</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>329069</t>
+          <t>365165</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>345277</t>
+          <t>382195</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5783,32 +5783,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>553979</t>
+          <t>378556</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>521996</t>
+          <t>367899</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>586172</t>
+          <t>389181</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5818,32 +5818,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>891852</t>
+          <t>753250</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>862751</t>
+          <t>739740</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>932166</t>
+          <t>766423</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>90,74%</t>
         </is>
       </c>
     </row>
@@ -5861,17 +5861,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>367009</t>
+          <t>405905</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>367009</t>
+          <t>405905</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>367009</t>
+          <t>405905</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5896,17 +5896,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>607958</t>
+          <t>438734</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>607958</t>
+          <t>438734</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>607958</t>
+          <t>438734</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5931,17 +5931,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>974968</t>
+          <t>844640</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>974968</t>
+          <t>844640</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>974968</t>
+          <t>844640</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5978,32 +5978,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>36952</t>
+          <t>39089</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28776</t>
+          <t>30441</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>47531</t>
+          <t>49134</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6013,32 +6013,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>113573</t>
+          <t>122738</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>101461</t>
+          <t>108845</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>128164</t>
+          <t>137605</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6048,32 +6048,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>150526</t>
+          <t>161827</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>133954</t>
+          <t>145813</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>167995</t>
+          <t>180644</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,39%</t>
         </is>
       </c>
     </row>
@@ -6091,32 +6091,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>42737</t>
+          <t>46524</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33447</t>
+          <t>36818</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>54215</t>
+          <t>58223</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6126,32 +6126,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>101345</t>
+          <t>110622</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>89442</t>
+          <t>97761</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>114657</t>
+          <t>124631</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6161,32 +6161,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>144082</t>
+          <t>157145</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>128265</t>
+          <t>140502</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>160774</t>
+          <t>174912</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,65%</t>
         </is>
       </c>
     </row>
@@ -6204,32 +6204,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>200861</t>
+          <t>222116</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>188058</t>
+          <t>208606</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>213006</t>
+          <t>234581</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6239,32 +6239,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>210912</t>
+          <t>231250</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>193780</t>
+          <t>216173</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>224919</t>
+          <t>247701</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6274,32 +6274,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>411773</t>
+          <t>453366</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>392924</t>
+          <t>431448</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>431169</t>
+          <t>473333</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>61,29%</t>
         </is>
       </c>
     </row>
@@ -6317,17 +6317,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>280550</t>
+          <t>307729</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>280550</t>
+          <t>307729</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>280550</t>
+          <t>307729</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6352,17 +6352,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6387,17 +6387,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>706381</t>
+          <t>772338</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>706381</t>
+          <t>772338</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>706381</t>
+          <t>772338</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6434,32 +6434,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>45908</t>
+          <t>48232</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36958</t>
+          <t>38721</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>56763</t>
+          <t>61187</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6469,32 +6469,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>128602</t>
+          <t>139614</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>69445</t>
+          <t>123176</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>168497</t>
+          <t>156893</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6504,32 +6504,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>174510</t>
+          <t>187845</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>109247</t>
+          <t>169808</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>205470</t>
+          <t>209385</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>
@@ -6547,32 +6547,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>62917</t>
+          <t>68592</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52236</t>
+          <t>55484</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76092</t>
+          <t>82390</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6582,32 +6582,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>140296</t>
+          <t>153924</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>79616</t>
+          <t>138272</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>181241</t>
+          <t>170535</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6617,32 +6617,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>203214</t>
+          <t>222516</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>134489</t>
+          <t>202224</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>240096</t>
+          <t>244994</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -6660,32 +6660,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>538733</t>
+          <t>596811</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>520923</t>
+          <t>578628</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>551037</t>
+          <t>611549</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6695,32 +6695,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>764891</t>
+          <t>609806</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>688914</t>
+          <t>589714</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>884748</t>
+          <t>628849</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6730,32 +6730,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1303624</t>
+          <t>1206617</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1241326</t>
+          <t>1180412</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1438997</t>
+          <t>1233361</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>76,28%</t>
         </is>
       </c>
     </row>
@@ -6773,17 +6773,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>647559</t>
+          <t>713635</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>647559</t>
+          <t>713635</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>647559</t>
+          <t>713635</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6808,17 +6808,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1033789</t>
+          <t>903343</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1033789</t>
+          <t>903343</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1033789</t>
+          <t>903343</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6843,17 +6843,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1681348</t>
+          <t>1616978</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1681348</t>
+          <t>1616978</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1681348</t>
+          <t>1616978</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
